--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.45271463839124</v>
+        <v>9.823566128738577</v>
       </c>
       <c r="D2" t="n">
-        <v>21.26810052661772</v>
+        <v>3.456066335575379</v>
       </c>
       <c r="E2" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F2" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.23610252712212</v>
+        <v>1.825866660657344</v>
       </c>
       <c r="D3" t="n">
-        <v>11.3528939122875</v>
+        <v>1.844845260746719</v>
       </c>
       <c r="E3" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F3" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.23376475020416</v>
+        <v>4.750486771908175</v>
       </c>
       <c r="D4" t="n">
-        <v>25.1483414295214</v>
+        <v>4.086605482297228</v>
       </c>
       <c r="E4" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F4" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.5266923357533</v>
+        <v>2.035587504559911</v>
       </c>
       <c r="D5" t="n">
-        <v>12.3807359639407</v>
+        <v>2.011869594140363</v>
       </c>
       <c r="E5" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F5" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.77323843059494</v>
+        <v>8.900651244971678</v>
       </c>
       <c r="D6" t="n">
-        <v>26.64479395180598</v>
+        <v>4.329779017168472</v>
       </c>
       <c r="E6" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F6" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.18650072552941</v>
+        <v>3.767806367898529</v>
       </c>
       <c r="D7" t="n">
-        <v>24.48512394576296</v>
+        <v>3.978832641186482</v>
       </c>
       <c r="E7" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F7" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.63141428525135</v>
+        <v>2.702604821353344</v>
       </c>
       <c r="D8" t="n">
-        <v>29.07939871828402</v>
+        <v>4.725402291721153</v>
       </c>
       <c r="E8" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F8" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.04357639401034</v>
+        <v>2.119581164026681</v>
       </c>
       <c r="D9" t="n">
-        <v>32.1429526042164</v>
+        <v>5.223229798185166</v>
       </c>
       <c r="E9" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F9" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.28721733889781</v>
+        <v>2.159172817570894</v>
       </c>
       <c r="D10" t="n">
-        <v>9.362992124477561</v>
+        <v>1.521486220227604</v>
       </c>
       <c r="E10" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F10" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.57764953656833</v>
+        <v>3.831368049692353</v>
       </c>
       <c r="D11" t="n">
-        <v>26.7201501691552</v>
+        <v>4.34202440248772</v>
       </c>
       <c r="E11" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F11" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.90124195827451</v>
+        <v>7.458951818219608</v>
       </c>
       <c r="D12" t="n">
-        <v>28.95377302703682</v>
+        <v>4.704988116893483</v>
       </c>
       <c r="E12" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F12" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50.75001121351531</v>
+        <v>8.246876822196239</v>
       </c>
       <c r="D13" t="n">
-        <v>31.16886567860688</v>
+        <v>5.064940672773618</v>
       </c>
       <c r="E13" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F13" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>50.73382740793694</v>
+        <v>8.244246953789752</v>
       </c>
       <c r="D14" t="n">
-        <v>29.67395748348998</v>
+        <v>4.822018091067122</v>
       </c>
       <c r="E14" t="n">
-        <v>17.81855687000708</v>
+        <v>2.89551549137615</v>
       </c>
       <c r="F14" t="n">
-        <v>7.50301190817548</v>
+        <v>1.219239435078515</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
